--- a/data/trans_orig/P36BPD13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023</t>
+          <t>Población según si consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>434932</t>
+          <t>435603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>462561</t>
+          <t>462948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647282</t>
+          <t>647539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>675399</t>
+          <t>675240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1091798</t>
+          <t>1093014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1132793</t>
+          <t>1131336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49449</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77078</t>
+          <t>76407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74993</t>
+          <t>75152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103110</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129608</t>
+          <t>131065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170603</t>
+          <t>169387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1874260</t>
+          <t>1878330</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2028298</t>
+          <t>2032768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1936006</t>
+          <t>1937356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2042025</t>
+          <t>2046409</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3830337</t>
+          <t>3832682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4035538</t>
+          <t>4030364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>249860</t>
+          <t>245390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403898</t>
+          <t>399828</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>185850</t>
+          <t>181466</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291869</t>
+          <t>290519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470495</t>
+          <t>475669</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675696</t>
+          <t>673351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>525753</t>
+          <t>525953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>565611</t>
+          <t>564537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>573783</t>
+          <t>570221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>600590</t>
+          <t>598736</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1109174</t>
+          <t>1108621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1158101</t>
+          <t>1156177</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76310</t>
+          <t>77384</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116168</t>
+          <t>115968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75360</t>
+          <t>78922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>134887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181890</t>
+          <t>182443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2875097</t>
+          <t>2864470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3040432</t>
+          <t>3036856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3182882</t>
+          <t>3178306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3298780</t>
+          <t>3297920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6078276</t>
+          <t>6073629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6276506</t>
+          <t>6267719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>391657</t>
+          <t>395233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>556992</t>
+          <t>567619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328630</t>
+          <t>329490</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>444528</t>
+          <t>449104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>782992</t>
+          <t>791779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>981222</t>
+          <t>985869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD13_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD13_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>450103</t>
+          <t>505979</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>435603</t>
+          <t>490245</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>462948</t>
+          <t>521497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>662404</t>
+          <t>721891</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>647539</t>
+          <t>706585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>675240</t>
+          <t>735449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1112506</t>
+          <t>1227870</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1093014</t>
+          <t>1205738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1131336</t>
+          <t>1248715</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61907</t>
+          <t>69482</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49062</t>
+          <t>53964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>76407</t>
+          <t>85216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87988</t>
+          <t>94541</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75152</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>102853</t>
+          <t>109847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149895</t>
+          <t>164023</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131065</t>
+          <t>143178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>169387</t>
+          <t>186155</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512010</t>
+          <t>575461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512010</t>
+          <t>575461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512010</t>
+          <t>575461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>750392</t>
+          <t>816432</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>750392</t>
+          <t>816432</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>750392</t>
+          <t>816432</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262401</t>
+          <t>1391893</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262401</t>
+          <t>1391893</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262401</t>
+          <t>1391893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1933458</t>
+          <t>1847203</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1878330</t>
+          <t>1804141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2032768</t>
+          <t>1888057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1977766</t>
+          <t>1875804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1937356</t>
+          <t>1842227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2046409</t>
+          <t>1903521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3911224</t>
+          <t>3723007</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3832682</t>
+          <t>3670241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4030364</t>
+          <t>3772107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>344700</t>
+          <t>370749</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>245390</t>
+          <t>329895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399828</t>
+          <t>413811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>250109</t>
+          <t>283262</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>181466</t>
+          <t>255545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290519</t>
+          <t>316839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>594809</t>
+          <t>654010</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>475669</t>
+          <t>604910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>673351</t>
+          <t>706776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2278158</t>
+          <t>2217952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2278158</t>
+          <t>2217952</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2278158</t>
+          <t>2217952</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2227875</t>
+          <t>2159066</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2227875</t>
+          <t>2159066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2227875</t>
+          <t>2159066</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4506033</t>
+          <t>4377017</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4506033</t>
+          <t>4377017</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4506033</t>
+          <t>4377017</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>547872</t>
+          <t>606763</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>525953</t>
+          <t>582597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>564537</t>
+          <t>624181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>586591</t>
+          <t>648475</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>570221</t>
+          <t>633980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>598736</t>
+          <t>663451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1134463</t>
+          <t>1255240</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1108621</t>
+          <t>1227403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1156177</t>
+          <t>1279942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94049</t>
+          <t>100118</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77384</t>
+          <t>82700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115968</t>
+          <t>124284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62552</t>
+          <t>74591</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>59615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78922</t>
+          <t>89086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>156601</t>
+          <t>174708</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134887</t>
+          <t>150006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182443</t>
+          <t>202545</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>641921</t>
+          <t>706881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>641921</t>
+          <t>706881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>641921</t>
+          <t>706881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>649143</t>
+          <t>723066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>649143</t>
+          <t>723066</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>649143</t>
+          <t>723066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1291064</t>
+          <t>1429948</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1291064</t>
+          <t>1429948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1291064</t>
+          <t>1429948</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2931434</t>
+          <t>2959946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2864470</t>
+          <t>2913205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3036856</t>
+          <t>3011081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3226761</t>
+          <t>3246171</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3178306</t>
+          <t>3205933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3297920</t>
+          <t>3279276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6158193</t>
+          <t>6206117</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6073629</t>
+          <t>6141828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6267719</t>
+          <t>6263390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>500655</t>
+          <t>540348</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>395233</t>
+          <t>489213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>567619</t>
+          <t>587089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>400649</t>
+          <t>452393</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329490</t>
+          <t>419288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>449104</t>
+          <t>492631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>901305</t>
+          <t>992741</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791779</t>
+          <t>935468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>985869</t>
+          <t>1057030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3432089</t>
+          <t>3500294</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3432089</t>
+          <t>3500294</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3432089</t>
+          <t>3500294</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3627410</t>
+          <t>3698564</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3627410</t>
+          <t>3698564</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3627410</t>
+          <t>3698564</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7059498</t>
+          <t>7198858</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7059498</t>
+          <t>7198858</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7059498</t>
+          <t>7198858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
